--- a/Result/profitability/2603.xlsx
+++ b/Result/profitability/2603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>9.8325</v>
+        <v>7.165</v>
       </c>
       <c r="N2" t="n">
-        <v>26.25375</v>
+        <v>22.52875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2725</v>
+        <v>5.413749999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.54875</v>
+        <v>18.98375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>3.84625</v>
       </c>
       <c r="N4" t="n">
-        <v>17.255</v>
+        <v>16.32125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>2.885</v>
+        <v>3.17875</v>
       </c>
       <c r="N5" t="n">
-        <v>13.29625</v>
+        <v>13.445</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>2.14125</v>
+        <v>1.8125</v>
       </c>
       <c r="N6" t="n">
-        <v>9.672499999999999</v>
+        <v>9.25375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8049999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="N7" t="n">
-        <v>5.553750000000001</v>
+        <v>6.16375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.84</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20875</v>
+        <v>0.655</v>
       </c>
       <c r="N8" t="n">
-        <v>2.19375</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0.03875000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9837500000000001</v>
+        <v>0.9837499999999997</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.21625</v>
       </c>
       <c r="N13" t="n">
-        <v>3.242500000000001</v>
+        <v>3.2425</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>105161</v>
+      </c>
+      <c r="D75" t="n">
+        <v>81183</v>
+      </c>
+      <c r="E75" t="n">
+        <v>23978</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>19358</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1507</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20864</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16034</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>10.74375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.7675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9296875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4738202973497092</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4644268774703559</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.190000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05506709856547909</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
